--- a/Result/profitability/1102.xlsx
+++ b/Result/profitability/1102.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.05</v>
       </c>
       <c r="M2" t="n">
-        <v>0.7899999999999999</v>
+        <v>0.915</v>
       </c>
       <c r="N2" t="n">
-        <v>14.93875</v>
+        <v>14.91125</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.84</v>
       </c>
       <c r="M3" t="n">
-        <v>0.82375</v>
+        <v>0.8774999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>15.60875</v>
+        <v>15.11375</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.58</v>
       </c>
       <c r="M4" t="n">
-        <v>0.7537499999999999</v>
+        <v>0.89875</v>
       </c>
       <c r="N4" t="n">
-        <v>14.71625</v>
+        <v>14.7025</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,16 +1018,16 @@
         <v>0.16</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7225</v>
+        <v>0.8087500000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>14.67625</v>
+        <v>14.0975</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.55</v>
       </c>
       <c r="M6" t="n">
-        <v>0.68125</v>
+        <v>0.73625</v>
       </c>
       <c r="N6" t="n">
-        <v>14.45125</v>
+        <v>14.14125</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>1.02</v>
       </c>
       <c r="M7" t="n">
-        <v>0.6675</v>
+        <v>0.79125</v>
       </c>
       <c r="N7" t="n">
-        <v>15.17125</v>
+        <v>15.17625</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,13 +1391,13 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>0.68125</v>
+        <v>0.8075</v>
       </c>
       <c r="N8" t="n">
-        <v>16.13125</v>
+        <v>16.17875</v>
       </c>
       <c r="O8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
@@ -1409,7 +1409,7 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -1518,7 +1518,7 @@
         <v>0.43</v>
       </c>
       <c r="M9" t="n">
-        <v>0.6649999999999999</v>
+        <v>0.665</v>
       </c>
       <c r="N9" t="n">
         <v>15.5175</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1102</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>18743</v>
+      </c>
+      <c r="D75" t="n">
+        <v>16242</v>
+      </c>
+      <c r="E75" t="n">
+        <v>2501</v>
+      </c>
+      <c r="F75" t="n">
+        <v>13.34</v>
+      </c>
+      <c r="G75" t="n">
+        <v>1711</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>9.13%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>3812</v>
+      </c>
+      <c r="J75" t="n">
+        <v>5523</v>
+      </c>
+      <c r="K75" t="n">
+        <v>5227</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.855</v>
+      </c>
+      <c r="N75" t="n">
+        <v>14.7125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X75" t="n">
+        <v>1.803571428571428</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.379999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.02932098765432101</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.7840909090909092</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-4.629999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.2576516416249304</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
